--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.77969149018886</v>
+        <v>7.60169986715569</v>
       </c>
       <c r="D2" t="n">
-        <v>46.95471305464157</v>
+        <v>7.630140871379256</v>
       </c>
       <c r="E2" t="n">
-        <v>10.8137719790391</v>
+        <v>1.757237946593854</v>
       </c>
       <c r="F2" t="n">
-        <v>10.83671051148896</v>
+        <v>1.760965458116956</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.73202348329489</v>
+        <v>8.40645381603542</v>
       </c>
       <c r="D3" t="n">
-        <v>51.57546504797428</v>
+        <v>8.38101307029582</v>
       </c>
       <c r="E3" t="n">
-        <v>10.8137719790391</v>
+        <v>1.757237946593854</v>
       </c>
       <c r="F3" t="n">
-        <v>10.83671051148896</v>
+        <v>1.760965458116956</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.27944425717589</v>
+        <v>4.757909691791083</v>
       </c>
       <c r="D4" t="n">
-        <v>29.37559682608829</v>
+        <v>4.773534484239347</v>
       </c>
       <c r="E4" t="n">
-        <v>10.8137719790391</v>
+        <v>1.757237946593854</v>
       </c>
       <c r="F4" t="n">
-        <v>10.83671051148896</v>
+        <v>1.760965458116956</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>15.40299593239725</v>
+        <v>2.502986839014554</v>
       </c>
       <c r="D5" t="n">
-        <v>15.34719512541451</v>
+        <v>2.493919207879858</v>
       </c>
       <c r="E5" t="n">
-        <v>10.8137719790391</v>
+        <v>1.757237946593854</v>
       </c>
       <c r="F5" t="n">
-        <v>10.83671051148896</v>
+        <v>1.760965458116956</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.99146004216187</v>
+        <v>4.873612256851303</v>
       </c>
       <c r="D6" t="n">
-        <v>29.81359381943371</v>
+        <v>4.844708995657978</v>
       </c>
       <c r="E6" t="n">
-        <v>10.8137719790391</v>
+        <v>1.757237946593854</v>
       </c>
       <c r="F6" t="n">
-        <v>10.83671051148896</v>
+        <v>1.760965458116956</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.60413849948744</v>
+        <v>5.135672506166709</v>
       </c>
       <c r="D7" t="n">
-        <v>31.36222285205916</v>
+        <v>5.096361213459613</v>
       </c>
       <c r="E7" t="n">
-        <v>10.8137719790391</v>
+        <v>1.757237946593854</v>
       </c>
       <c r="F7" t="n">
-        <v>10.83671051148896</v>
+        <v>1.760965458116956</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.11648881804026</v>
+        <v>4.731429432931543</v>
       </c>
       <c r="D8" t="n">
-        <v>28.96272664851671</v>
+        <v>4.706443080383966</v>
       </c>
       <c r="E8" t="n">
-        <v>10.8137719790391</v>
+        <v>1.757237946593854</v>
       </c>
       <c r="F8" t="n">
-        <v>10.83671051148896</v>
+        <v>1.760965458116956</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.69417525141156</v>
+        <v>6.61280347835438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.64069321985623</v>
+        <v>6.604112648226637</v>
       </c>
       <c r="E9" t="n">
-        <v>10.8137719790391</v>
+        <v>1.757237946593854</v>
       </c>
       <c r="F9" t="n">
-        <v>10.83671051148896</v>
+        <v>1.760965458116956</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
